--- a/InputData/fuels/BCTR/BAU Carbon Tax Rate.xlsx
+++ b/InputData/fuels/BCTR/BAU Carbon Tax Rate.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anaxolt/Google Drive/2021/D.Development/TARGET_eps-us-3.2.1/InputData/fuels/BCTR/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rod\Desktop\EPS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B93C6C-45F4-464E-8ED4-9465B14F521C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC815C93-D4ED-441E-929F-D47112F2A487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-80" yWindow="500" windowWidth="23960" windowHeight="16500" xr2:uid="{A875A243-FD0C-4B21-82AE-BAE80D34FF17}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{A875A243-FD0C-4B21-82AE-BAE80D34FF17}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="BCTR" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,6 +27,9 @@
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -40,6 +43,33 @@
   </si>
   <si>
     <t>Source:</t>
+  </si>
+  <si>
+    <t>Servicio de Administración Tributaria</t>
+  </si>
+  <si>
+    <t>Impuesto a los combustibles fósiles</t>
+  </si>
+  <si>
+    <t>http://www.sat.gob.mx/fichas_tematicas/reforma_fiscal/Paginas/combustibles_fosiles_2014.aspx</t>
+  </si>
+  <si>
+    <t>http://m.sat.gob.mx/fichas_tematicas/reforma_fiscal/Paginas/combustibles_fosiles_2014.aspx</t>
+  </si>
+  <si>
+    <t>Weighted rate</t>
+  </si>
+  <si>
+    <t>USD/MtCO2e</t>
+  </si>
+  <si>
+    <t>Carbon tax rate</t>
+  </si>
+  <si>
+    <t>Fuel share</t>
+  </si>
+  <si>
+    <t>of fuel share</t>
   </si>
   <si>
     <t>Notes</t>
@@ -70,33 +100,6 @@
   </si>
   <si>
     <t>geoengineering sector (uses industry sector rate)</t>
-  </si>
-  <si>
-    <t>Servicio de Administración Tributaria</t>
-  </si>
-  <si>
-    <t>Impuesto a los combustibles fósiles</t>
-  </si>
-  <si>
-    <t>http://www.sat.gob.mx/fichas_tematicas/reforma_fiscal/Paginas/combustibles_fosiles_2014.aspx</t>
-  </si>
-  <si>
-    <t>http://m.sat.gob.mx/fichas_tematicas/reforma_fiscal/Paginas/combustibles_fosiles_2014.aspx</t>
-  </si>
-  <si>
-    <t>USD/MtCO2e</t>
-  </si>
-  <si>
-    <t>Weighted rate</t>
-  </si>
-  <si>
-    <t>Fuel share</t>
-  </si>
-  <si>
-    <t>Carbon tax rate</t>
-  </si>
-  <si>
-    <t>of fuel share</t>
   </si>
 </sst>
 </file>
@@ -193,7 +196,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -210,9 +213,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -250,7 +253,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -356,7 +359,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -498,7 +501,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -507,93 +510,93 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49357908-BC85-41CC-9D98-173369A13AF6}">
   <dimension ref="A1:C30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="5">
         <v>2014</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="7" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="6" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="B10" s="8">
         <f>B12*B13</f>
         <v>0.99</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="B12" s="8">
         <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B13" s="9">
         <v>0.33</v>
       </c>
       <c r="C13" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B17" s="1"/>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B21" s="6"/>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
     </row>
   </sheetData>
@@ -611,15 +614,15 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AG9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:BA9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B1" s="1">
         <v>2019</v>
@@ -717,10 +720,70 @@
       <c r="AG1" s="1">
         <v>2050</v>
       </c>
+      <c r="AH1" s="1">
+        <v>2051</v>
+      </c>
+      <c r="AI1" s="1">
+        <v>2052</v>
+      </c>
+      <c r="AJ1" s="1">
+        <v>2053</v>
+      </c>
+      <c r="AK1" s="1">
+        <v>2054</v>
+      </c>
+      <c r="AL1" s="1">
+        <v>2055</v>
+      </c>
+      <c r="AM1" s="1">
+        <v>2056</v>
+      </c>
+      <c r="AN1" s="1">
+        <v>2057</v>
+      </c>
+      <c r="AO1" s="1">
+        <v>2058</v>
+      </c>
+      <c r="AP1" s="1">
+        <v>2059</v>
+      </c>
+      <c r="AQ1" s="1">
+        <v>2060</v>
+      </c>
+      <c r="AR1" s="1">
+        <v>2061</v>
+      </c>
+      <c r="AS1" s="1">
+        <v>2062</v>
+      </c>
+      <c r="AT1" s="1">
+        <v>2063</v>
+      </c>
+      <c r="AU1" s="1">
+        <v>2064</v>
+      </c>
+      <c r="AV1" s="1">
+        <v>2065</v>
+      </c>
+      <c r="AW1" s="1">
+        <v>2066</v>
+      </c>
+      <c r="AX1" s="1">
+        <v>2067</v>
+      </c>
+      <c r="AY1" s="1">
+        <v>2068</v>
+      </c>
+      <c r="AZ1" s="1">
+        <v>2069</v>
+      </c>
+      <c r="BA1" s="1">
+        <v>2070</v>
+      </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B2" s="10">
         <f>About!$B$10</f>
@@ -850,10 +913,90 @@
         <f t="shared" si="0"/>
         <v>0.99</v>
       </c>
+      <c r="AH2">
+        <f>AG2</f>
+        <v>0.99</v>
+      </c>
+      <c r="AI2">
+        <f t="shared" ref="AI2:BA9" si="1">AH2</f>
+        <v>0.99</v>
+      </c>
+      <c r="AJ2">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AK2">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AL2">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AM2">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AN2">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AO2">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AP2">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AQ2">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AR2">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AS2">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AT2">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AU2">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AV2">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AW2">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AX2">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AY2">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AZ2">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="BA2">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -951,10 +1094,90 @@
       <c r="AG3">
         <v>0</v>
       </c>
+      <c r="AH3">
+        <f t="shared" ref="AH3:AW9" si="2">AG3</f>
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BA3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B4" s="10">
         <f>About!$B$10</f>
@@ -1084,10 +1307,90 @@
         <f t="shared" si="0"/>
         <v>0.99</v>
       </c>
+      <c r="AH4">
+        <f t="shared" si="2"/>
+        <v>0.99</v>
+      </c>
+      <c r="AI4">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AJ4">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AK4">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AL4">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AM4">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AN4">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AO4">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AP4">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AQ4">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AR4">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AS4">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AT4">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AU4">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AV4">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AW4">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AX4">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AY4">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AZ4">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="BA4">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B5" s="10">
         <f>About!$B$10</f>
@@ -1217,143 +1520,303 @@
         <f t="shared" si="0"/>
         <v>0.99</v>
       </c>
+      <c r="AH5">
+        <f t="shared" si="2"/>
+        <v>0.99</v>
+      </c>
+      <c r="AI5">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AJ5">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AK5">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AL5">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AM5">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AN5">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AO5">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AP5">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AQ5">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AR5">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AS5">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AT5">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AU5">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AV5">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AW5">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AX5">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AY5">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AZ5">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="BA5">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B6" s="10">
         <f>About!$B$10</f>
         <v>0.99</v>
       </c>
       <c r="C6">
-        <f t="shared" ref="C6:AG6" si="1">B6</f>
+        <f t="shared" ref="C6:AG6" si="3">B6</f>
         <v>0.99</v>
       </c>
       <c r="D6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.99</v>
       </c>
       <c r="E6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.99</v>
       </c>
       <c r="F6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.99</v>
       </c>
       <c r="G6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.99</v>
       </c>
       <c r="H6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.99</v>
       </c>
       <c r="I6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.99</v>
       </c>
       <c r="J6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.99</v>
       </c>
       <c r="K6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.99</v>
       </c>
       <c r="L6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.99</v>
       </c>
       <c r="M6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.99</v>
       </c>
       <c r="N6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.99</v>
       </c>
       <c r="O6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.99</v>
       </c>
       <c r="P6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.99</v>
       </c>
       <c r="Q6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.99</v>
       </c>
       <c r="R6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.99</v>
       </c>
       <c r="S6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.99</v>
       </c>
       <c r="T6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.99</v>
       </c>
       <c r="U6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.99</v>
       </c>
       <c r="V6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.99</v>
       </c>
       <c r="W6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.99</v>
       </c>
       <c r="X6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.99</v>
       </c>
       <c r="Y6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.99</v>
       </c>
       <c r="Z6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.99</v>
       </c>
       <c r="AA6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.99</v>
       </c>
       <c r="AB6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.99</v>
       </c>
       <c r="AC6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.99</v>
       </c>
       <c r="AD6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.99</v>
       </c>
       <c r="AE6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.99</v>
       </c>
       <c r="AF6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.99</v>
       </c>
       <c r="AG6">
+        <f t="shared" si="3"/>
+        <v>0.99</v>
+      </c>
+      <c r="AH6">
+        <f t="shared" si="2"/>
+        <v>0.99</v>
+      </c>
+      <c r="AI6">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AJ6">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AK6">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AL6">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AM6">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AN6">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AO6">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AP6">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AQ6">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AR6">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AS6">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AT6">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AU6">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AV6">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AW6">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AX6">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AY6">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="AZ6">
+        <f t="shared" si="1"/>
+        <v>0.99</v>
+      </c>
+      <c r="BA6">
         <f t="shared" si="1"/>
         <v>0.99</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -1451,10 +1914,90 @@
       <c r="AG7">
         <v>0</v>
       </c>
+      <c r="AH7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
@@ -1552,10 +2095,90 @@
       <c r="AG8" s="3">
         <v>0</v>
       </c>
+      <c r="AH8" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AI8" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK8" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL8" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM8" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN8" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO8" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP8" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR8" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS8" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT8" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU8" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV8" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW8" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX8" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY8" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ8" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BA8" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B9" s="3">
         <v>0</v>
@@ -1651,6 +2274,86 @@
         <v>0</v>
       </c>
       <c r="AG9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AI9" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK9" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL9" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM9" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN9" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO9" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP9" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR9" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS9" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT9" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU9" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV9" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW9" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX9" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY9" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ9" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BA9" s="3">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -1658,4 +2361,184 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="2675f8417a7852adb5ac278d647999f1">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1d431266b3277f48244cbeea34d4f4da" ns2:_="">
+    <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="79748b23-d81a-423e-9112-21109dc864e6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFFC77B5-FC08-43CC-800A-F5202351B438}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9116EE90-33BE-4DBE-9D35-2D5381F677D5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C16C809F-ABD3-4361-9054-9477A0679996}"/>
 </file>